--- a/dugnad/sjekkpakker/OKO-07.xlsx
+++ b/dugnad/sjekkpakker/OKO-07.xlsx
@@ -29,12 +29,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="127">
   <si>
     <t>Sjekkpakke OKO-07: Overvåking og algoritmisk ledelse på arbeidsplassen</t>
   </si>
   <si>
-    <t>Laget 2026-10-27 · 7 påstander · Uregulert KI (arbeidstittel)</t>
+    <t>Laget 2026-10-27 · 10 påstander · Uregulert KI (arbeidstittel)</t>
   </si>
   <si>
     <t>Sjekket av</t>
@@ -172,7 +172,7 @@
     <t>Du kan bruke KI til å finne kilder, oppsummere og peke deg til rett sted i kilden. Men selve sjekken gjør du selv ved å lese originalen. Uten menneskelig verifisering er dugnaden verdiløs.</t>
   </si>
   <si>
-    <t>Privatpersoner navngis aldri.</t>
+    <t>Privatpersoner i privat rolle navngis aldri. Forskere og fagpersoner som uttaler seg offentlig i fagrollen sin, kan navngis.</t>
   </si>
   <si>
     <t>Spørsmål?</t>
@@ -333,13 +333,99 @@
   </si>
   <si>
     <t>ikke verifisert · Lagt til 2026-10-21 (OKO-07). Sjekk mot Datatilsynets årsrapport. · Eksistens (2026-10-25): usikker – Tallene (1 800 henvendelser, 73 klager for 2018) er omtalt av SecurityWorldMarket 25.6.2019 med DN som kilde, men hvilken av disse sidene det er, er uklart; titler ikke sett ordrett. Kandidater: https://www.securityworldmarket.com/no/Nyhetsarkiv/bekymret-for-okt-overvakning-pa-jobb ; https://www.sec</t>
+  </si>
+  <si>
+    <t>OKO-07.P08</t>
+  </si>
+  <si>
+    <t>Algoritmisk ledelse kan gi økt arbeidspress og mindre autonomi for ansatte</t>
+  </si>
+  <si>
+    <t>K1211</t>
+  </si>
+  <si>
+    <t>Bragtvedt og Arora (Nordlandsforskning og Vestlandsforskning) (2026) – Kunstig intelligens, algoritmisk ledelse og arbeidsliv. En litteraturgjennomgang (NF-rapport 7/2026) · Nordlandsforskning</t>
+  </si>
+  <si>
+    <t>https://www.regjeringen.no/contentassets/028e024f34564666a145c083339592b1/ki-og-arbeidsliv-juni-2026.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ny norsk kunnskapsoppsummering (2026): algoritmisk ledelse kan gi økt arbeidstempo, mindre autonomi, svakere kollegiale relasjoner og et ansvarsgap der ansatte står ansvarlige for beslutninger de ikke kan forklare eller påvirke [K1211] [K1212].
+Plattformøkonomien som laboratorium: styringsformene derfra kan spre seg til logistikk, lager, kundesenter og industri [K1211].
+Orienteringssak, ikke forhandling: ved ett norsk universitet ble et opptaksverktøy med omfattende datalagring bare tatt opp som orienteringssak, uten at fagforeningene fikk påvirke beslutningen [K1211].
+Regelverket fanger ikke maktforholdene: GDPR retter seg mot innsamlingen av data, ikke mot analysen og styringen. KI-forordningen lar leverandøren selv vurdere risikoen, og plattformdirektivet gjelder bare plattformarbeid [K1211] [K1213].
+Forslag fra forskningen: forby automatiske oppsigelser og overvåking av private rom på arbeidsplassen, flytt bevisbyrden for at systemene ikke diskriminerer over på arbeidsgiver eller leverandør, og gi tillitsvalgte rett til eksperthjelp betalt av arbeidsgiver, slik tyske bedriftsråd har hatt siden 2021 [K1211] (OKO-19).
+Overvekt av risiko: Nordlandsforskning påpeker selv at gjennomgangen har en overvekt av studier om risiko, blant annet fordi produktivitet var holdt utenfor [K1211].</t>
+  </si>
+  <si>
+    <t>ikke verifisert · Lagt til 2026-10-27 (REG-02). Oppdrag fra AID. Narrativ gjennomgang av 100 artikler; overvekt av studier om risiko, produktivitet holdt utenfor.</t>
+  </si>
+  <si>
+    <t>K1212</t>
+  </si>
+  <si>
+    <t>Arbeids- og inkluderingsdepartementet og Digitaliserings- og forvaltningsdepartementet (2026) – Ny rapport: KI kan utfordre arbeidsmiljøet · regjeringen.no</t>
+  </si>
+  <si>
+    <t>https://www.regjeringen.no/no/aktuelt/ny-rapport-ki-kan-utfordre-arbeidsmiljoet/id3167552/</t>
+  </si>
+  <si>
+    <t>Ny norsk kunnskapsoppsummering (2026): algoritmisk ledelse kan gi økt arbeidstempo, mindre autonomi, svakere kollegiale relasjoner og et ansvarsgap der ansatte står ansvarlige for beslutninger de ikke kan forklare eller påvirke [K1211] [K1212].</t>
+  </si>
+  <si>
+    <t>ikke verifisert · Lagt til 2026-10-27 (REG-02). Publisert 25.06.2026.</t>
+  </si>
+  <si>
+    <t>OKO-07.P09</t>
+  </si>
+  <si>
+    <t>Over halvparten av norske bedrifter drøfter ikke bruk av digitale verktøy med de tillitsvalgte</t>
+  </si>
+  <si>
+    <t>K1213</t>
+  </si>
+  <si>
+    <t>Arbeidstilsynet (2026) – Utsikt, 4. utgave (2026) · Arbeidstilsynet</t>
+  </si>
+  <si>
+    <t>https://www.arbeidstilsynet.no/globalassets/rapportar/utsikt/utsikt-utgave-4.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sjefsvare i Europa: 12 % av europeiske virksomheter sporer innhold og tempo i arbeidet, og 8 % overvåker ansattes prestasjoner [K1213].
+Tillitsvalgte holdes utenfor: over halvparten av bedriftene drøfter ikke bruk av digitale verktøy med de tillitsvalgte. I 2021 var tillitsvalgte eller verneombud med på innføringen av ny teknologi i bare 34–36 % av virksomhetene [K1213].
+Regelverket fanger ikke maktforholdene: GDPR retter seg mot innsamlingen av data, ikke mot analysen og styringen. KI-forordningen lar leverandøren selv vurdere risikoen, og plattformdirektivet gjelder bare plattformarbeid [K1211] [K1213].
+Myndighetene har justert seg: i 2025 skrev Arbeidstilsynet at det er «utelukkende positivt» for arbeidstakeren når ny teknologi bistår i arbeidet [K1214]. I 2026 står det «kan være positivt» [K1213].</t>
+  </si>
+  <si>
+    <t>ikke verifisert · Lagt til 2026-10-27 (REG-02).</t>
+  </si>
+  <si>
+    <t>OKO-07.P10</t>
+  </si>
+  <si>
+    <t>Arbeidstilsynet skrev i 2025 at teknologi som bistår arbeidstakeren, er utelukkende positivt, men nyanserte dette i 2026</t>
+  </si>
+  <si>
+    <t>K1214</t>
+  </si>
+  <si>
+    <t>Arbeidstilsynet (2025) – Utsikt, 3. utgave (2025) · Arbeidstilsynet</t>
+  </si>
+  <si>
+    <t>https://www.arbeidstilsynet.no/globalassets/rapportar/utsikt/utsikt-utgave-3.pdf</t>
+  </si>
+  <si>
+    <t>Myndighetene har justert seg: i 2025 skrev Arbeidstilsynet at det er «utelukkende positivt» for arbeidstakeren når ny teknologi bistår i arbeidet [K1214]. I 2026 står det «kan være positivt» [K1213].</t>
+  </si>
+  <si>
+    <t>ikke verifisert · Lagt til 2026-10-27 (REG-02). Brukt for sitatet s. 55 om at KI som bistår, er «utelukkende positivt».</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -365,6 +451,10 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF1F5FA8"/>
     </font>
   </fonts>
   <fills count="6">
@@ -407,7 +497,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -430,6 +520,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1029,7 +1122,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1360,9 +1453,166 @@
       <c r="P9" s="5"/>
       <c r="Q9" s="5"/>
     </row>
+    <row r="10" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="5"/>
+      <c r="Q10" s="5"/>
+    </row>
+    <row r="11" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="9"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="5"/>
+    </row>
+    <row r="12" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="5"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="5"/>
+      <c r="Q12" s="5"/>
+    </row>
+    <row r="13" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="5"/>
+    </row>
+    <row r="14" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="9"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="5"/>
+      <c r="Q14" s="5"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:Q1"/>
-  <mergeCells count="8">
+  <mergeCells count="24">
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="L2:L3"/>
@@ -1371,24 +1621,56 @@
     <mergeCell ref="O2:O3"/>
     <mergeCell ref="P2:P3"/>
     <mergeCell ref="Q2:Q3"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="L10:L11"/>
+    <mergeCell ref="M10:M11"/>
+    <mergeCell ref="N10:N11"/>
+    <mergeCell ref="O10:O11"/>
+    <mergeCell ref="P10:P11"/>
+    <mergeCell ref="Q10:Q11"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="P13:P14"/>
+    <mergeCell ref="Q13:Q14"/>
   </mergeCells>
-  <dataValidations count="5">
+  <dataValidations count="8">
+    <dataValidation type="list" allowBlank="1" sqref="H10:H14">
+      <formula1>"verifisert,delvis,sekundær,ikke funnet,feil"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="H2:H4">
       <formula1>"verifisert,delvis,sekundær,ikke funnet,feil"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="H6">
       <formula1>"verifisert,delvis,sekundær,ikke funnet,feil"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="H8:H9">
+    <dataValidation type="list" allowBlank="1" sqref="H8:H14">
       <formula1>"verifisert,delvis,sekundær,ikke funnet,feil"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J2:J9">
+    <dataValidation type="list" allowBlank="1" sqref="J10:J14">
       <formula1>"ja,nei,preprint"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L2:P9">
+    <dataValidation type="list" allowBlank="1" sqref="J2:J14">
+      <formula1>"ja,nei,preprint"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L10:P14">
+      <formula1>"0,1,2,3"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L2:P14">
       <formula1>"0,1,2,3"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="E10" r:id="rId1"/>
+    <hyperlink ref="E11" r:id="rId2"/>
+    <hyperlink ref="E12" r:id="rId3"/>
+    <hyperlink ref="E13" r:id="rId4"/>
+    <hyperlink ref="E14" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/dugnad/sjekkpakker/OKO-07.xlsx
+++ b/dugnad/sjekkpakker/OKO-07.xlsx
@@ -20,7 +20,7 @@
     <comment ref="B4" authorId="0">
       <text>
         <r>
-          <t>Kallenavn eller GitHub-navn. Det kan bli stående offentlig i kilderegisteret.</t>
+          <t>Navnet du vil stå med offentlig: fullt navn, kallenavn eller GitHub-navn. Det blir stående i kilderegisteret på GitHub og kan ikke fjernes helt i ettertid.</t>
         </r>
       </text>
     </comment>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="129">
   <si>
     <t>Sjekkpakke OKO-07: Overvåking og algoritmisk ledelse på arbeidsplassen</t>
   </si>
@@ -64,7 +64,10 @@
     <t>3</t>
   </si>
   <si>
-    <t>Les det som er relevant, og sammenlign med «Rapporten sier». Sett «Status» og skriv kort i «Om kilden» hvordan du sjekket og hva som eventuelt avviker.</t>
+    <t>Les det som er relevant, og sammenlign med «Rapporten sier». Sett «Status», og skriv i «Avvik» hvis noe avviker, ligger bak betalingsmur eller er uventet.</t>
+  </si>
+  <si>
+    <t>Er status «verifisert» eller «delvis», skriv i «Hvor i kilden» hvor det står: side (rapport, bok, artikkel), § og ledd (lov), artikkel og nummer (EU-rett), avsnitt (dom) eller overskrift (nettside). Da kan neste person slå rett opp.</t>
   </si>
   <si>
     <t>4</t>
@@ -94,13 +97,13 @@
     <t>verifisert</t>
   </si>
   <si>
-    <t>Du har åpnet primærkilden, og den sier det påstanden bygger på.</t>
+    <t>Du har lest det relevante i primærkilden, og den sier det påstanden bygger på.</t>
   </si>
   <si>
     <t>delvis</t>
   </si>
   <si>
-    <t>Stemmer, men med avvik. Skriv avviket i «Om kilden».</t>
+    <t>Stemmer, men med avvik. Skriv avviket i «Avvik».</t>
   </si>
   <si>
     <t>sekundær</t>
@@ -157,13 +160,13 @@
     <t>A Aktualitet</t>
   </si>
   <si>
-    <t>Er det fortsatt gyldig? 0 utdatert (motbevist, erstattet, loven endret) eller ikke sjekket · 1 usikker gyldighet (feltet har endret seg mye siden, f.eks. studier av eldre KI-modeller) · 2 gyldig, ingen kjent nyere forskning sier noe annet, uansett alder · 3 fersk (gjelder dagens situasjon) eller bekreftet av nyere forskning. Bekreftelsen kan stå i kommentaren.</t>
+    <t>Er det fortsatt gyldig? 0 utdatert (motbevist, erstattet, lovendring) eller ikke sjekket · 1 usikker gyldighet (feltet har endret seg mye siden, f.eks. studier av eldre KI-modeller) · 2 gyldig, ingen kjent nyere forskning sier noe annet, uansett alder · 3 fersk (gjelder dagens situasjon) eller bekreftet av nyere forskning. Bekreftelsen kan stå i kommentaren.</t>
   </si>
   <si>
     <t>Husk</t>
   </si>
   <si>
-    <t>Aldri dikt opp. Tall, datoer og navn tas fra kilden, ikke fra hukommelsen.</t>
+    <t>Ha integritet.</t>
   </si>
   <si>
     <t>Skill mellom «viser», «tyder på» og «antyder», og mellom én studie og konsensus. En påstand kan ha riktig kilde og likevel si mer enn kilden gjør.</t>
@@ -205,13 +208,16 @@
     <t>Status ▾</t>
   </si>
   <si>
+    <t>Hvor i kilden (s., §, art., avsnitt)</t>
+  </si>
+  <si>
     <t>Riktig eller ny lenke / DOI</t>
   </si>
   <si>
     <t>Fagfelle-vurdert ▾</t>
   </si>
   <si>
-    <t>Om kilden: hvordan du sjekket, hva som avviker</t>
+    <t>Avvik / betalingsmur / uventet</t>
   </si>
   <si>
     <t>E ▾</t>
@@ -425,6 +431,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+  </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
@@ -457,12 +466,17 @@
       <color rgb="FF1F5FA8"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEEEEE"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -485,7 +499,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -493,36 +507,66 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="hair"/>
+      <right style="hair"/>
+      <top style="hair"/>
+      <bottom style="hair"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -864,256 +908,291 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="90" customWidth="1"/>
+    <col min="2" max="2" width="91.45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="2"/>
+    </row>
+    <row r="2" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="B2" s="4"/>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+    </row>
+    <row r="4" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="B4" s="8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+      <c r="B5" s="9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="10"/>
+      <c r="B6" s="10"/>
+    </row>
+    <row r="7" spans="1:2" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="B7" s="12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+    <row r="9" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="13" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+    <row r="10" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="13" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+    <row r="11" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="3" t="s">
+    </row>
+    <row r="12" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+      <c r="B12" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="3" t="s">
+    </row>
+    <row r="13" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="B13" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="3" t="s">
+    </row>
+    <row r="14" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="13" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
+    <row r="15" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="10"/>
+      <c r="B16" s="10"/>
+    </row>
+    <row r="17" spans="1:2" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
+      <c r="B18" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="3" t="s">
+    </row>
+    <row r="19" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
+      <c r="B19" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="3" t="s">
+    </row>
+    <row r="20" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
+      <c r="B20" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="3" t="s">
+    </row>
+    <row r="21" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
+      <c r="B21" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="B21" s="3" t="s">
+    </row>
+    <row r="22" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="13" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
+    <row r="23" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B23" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="B24" s="6" t="s">
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="10"/>
+      <c r="B24" s="10"/>
+    </row>
+    <row r="25" spans="1:2" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="12" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
+      <c r="B25" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="B25" s="3" t="s">
+    </row>
+    <row r="26" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="7" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
+      <c r="B26" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="B26" s="3" t="s">
+    </row>
+    <row r="27" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
+      <c r="B27" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="3" t="s">
+    </row>
+    <row r="28" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
+      <c r="B28" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="B28" s="3" t="s">
+    </row>
+    <row r="29" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
+      <c r="B29" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="3" t="s">
+    </row>
+    <row r="30" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="6" t="s">
+      <c r="B30" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B32" s="3" t="s">
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="10"/>
+      <c r="B31" s="10"/>
+    </row>
+    <row r="32" spans="1:2" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="12" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B33" s="3" t="s">
+      <c r="B32" s="12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B33" s="13" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="34" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B34" s="3" t="s">
+    <row r="34" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B34" s="13" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="35" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B35" s="3" t="s">
+    <row r="35" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B35" s="13" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="36" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
+    <row r="36" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B36" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="B36" s="3" t="s">
+    </row>
+    <row r="37" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="7" t="s">
         <v>49</v>
       </c>
+      <c r="B37" s="13" t="s">
+        <v>50</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
   <legacyDrawing r:id="rId2"/>
@@ -1122,7 +1201,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1133,510 +1212,527 @@
     <col min="6" max="6" width="60" customWidth="1"/>
     <col min="7" max="7" width="36" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
-    <col min="9" max="9" width="26" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="36" customWidth="1"/>
-    <col min="12" max="16" width="5" customWidth="1"/>
-    <col min="17" max="17" width="40" customWidth="1"/>
+    <col min="9" max="9" width="18" customWidth="1"/>
+    <col min="10" max="10" width="26" customWidth="1"/>
+    <col min="11" max="11" width="11" customWidth="1"/>
+    <col min="12" max="12" width="36" customWidth="1"/>
+    <col min="13" max="17" width="5" customWidth="1"/>
+    <col min="18" max="18" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B1" s="7" t="s">
+    <row r="1" ht="32" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="B1" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="C1" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="D1" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="E1" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="F1" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="G1" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="H1" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="I1" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="J1" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="K1" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="L1" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="M1" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="N1" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="O1" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="Q1" s="8" t="s">
+      <c r="P1" s="15" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+      <c r="Q1" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="R1" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="C2" s="9" t="s">
+    </row>
+    <row r="2" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="B2" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="E2" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="9" t="s">
+      <c r="C2" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="D2" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-    </row>
-    <row r="3" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="9"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9" t="s">
+      <c r="E2" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="G2" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="E3" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" s="9" t="s">
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17"/>
+      <c r="R2" s="17"/>
+    </row>
+    <row r="3" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="16"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="D3" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="17"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="17"/>
+      <c r="R3" s="17"/>
+    </row>
+    <row r="4" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="17"/>
+    </row>
+    <row r="5" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="17"/>
+      <c r="M5" s="17"/>
+      <c r="N5" s="17"/>
+      <c r="O5" s="17"/>
+      <c r="P5" s="17"/>
+      <c r="Q5" s="17"/>
+      <c r="R5" s="17"/>
+    </row>
+    <row r="6" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="17"/>
+      <c r="N6" s="17"/>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+    </row>
+    <row r="7" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="17"/>
+      <c r="M7" s="17"/>
+      <c r="N7" s="17"/>
+      <c r="O7" s="17"/>
+      <c r="P7" s="17"/>
+      <c r="Q7" s="17"/>
+      <c r="R7" s="17"/>
+    </row>
+    <row r="8" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-    </row>
-    <row r="4" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="5"/>
-    </row>
-    <row r="5" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="5"/>
-    </row>
-    <row r="6" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="5"/>
-    </row>
-    <row r="7" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
-      <c r="P7" s="5"/>
-      <c r="Q7" s="5"/>
-    </row>
-    <row r="8" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-      <c r="P8" s="5"/>
-      <c r="Q8" s="5"/>
-    </row>
-    <row r="9" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="C9" s="9" t="s">
+      <c r="E8" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="H8" s="17"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="17"/>
+      <c r="N8" s="17"/>
+      <c r="O8" s="17"/>
+      <c r="P8" s="17"/>
+      <c r="Q8" s="17"/>
+      <c r="R8" s="17"/>
+    </row>
+    <row r="9" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="B9" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="E9" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="G9" s="9" t="s">
+      <c r="C9" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
-      <c r="N9" s="5"/>
-      <c r="O9" s="5"/>
-      <c r="P9" s="5"/>
-      <c r="Q9" s="5"/>
-    </row>
-    <row r="10" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
+      <c r="D9" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="E9" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="G9" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="17"/>
+      <c r="M9" s="17"/>
+      <c r="N9" s="17"/>
+      <c r="O9" s="17"/>
+      <c r="P9" s="17"/>
+      <c r="Q9" s="17"/>
+      <c r="R9" s="17"/>
+    </row>
+    <row r="10" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="B10" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="C10" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="D10" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="E10" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
-      <c r="N10" s="5"/>
-      <c r="O10" s="5"/>
-      <c r="P10" s="5"/>
-      <c r="Q10" s="5"/>
-    </row>
-    <row r="11" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9" t="s">
+      <c r="F10" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="G10" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="17"/>
+      <c r="M10" s="17"/>
+      <c r="N10" s="17"/>
+      <c r="O10" s="17"/>
+      <c r="P10" s="17"/>
+      <c r="Q10" s="17"/>
+      <c r="R10" s="17"/>
+    </row>
+    <row r="11" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="16"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="D11" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="E11" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="5"/>
-    </row>
-    <row r="12" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
+      <c r="F11" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="G11" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="17"/>
+      <c r="M11" s="17"/>
+      <c r="N11" s="17"/>
+      <c r="O11" s="17"/>
+      <c r="P11" s="17"/>
+      <c r="Q11" s="17"/>
+      <c r="R11" s="17"/>
+    </row>
+    <row r="12" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="B12" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="C12" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="D12" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="E12" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="5"/>
-      <c r="N12" s="5"/>
-      <c r="O12" s="5"/>
-      <c r="P12" s="5"/>
-      <c r="Q12" s="5"/>
-    </row>
-    <row r="13" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
+      <c r="F12" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="G12" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="17"/>
+      <c r="M12" s="17"/>
+      <c r="N12" s="17"/>
+      <c r="O12" s="17"/>
+      <c r="P12" s="17"/>
+      <c r="Q12" s="17"/>
+      <c r="R12" s="17"/>
+    </row>
+    <row r="13" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="B13" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="C13" s="16" t="s">
         <v>124</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="D13" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="G13" s="9" t="s">
+      <c r="E13" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="5"/>
-    </row>
-    <row r="14" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="E14" s="10" t="s">
+      <c r="F13" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="H13" s="17"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="17"/>
+      <c r="L13" s="17"/>
+      <c r="M13" s="17"/>
+      <c r="N13" s="17"/>
+      <c r="O13" s="17"/>
+      <c r="P13" s="17"/>
+      <c r="Q13" s="17"/>
+      <c r="R13" s="17"/>
+    </row>
+    <row r="14" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="16"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="D14" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="E14" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
-      <c r="M14" s="5"/>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
-      <c r="P14" s="5"/>
-      <c r="Q14" s="5"/>
+      <c r="F14" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="H14" s="17"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="17"/>
+      <c r="L14" s="17"/>
+      <c r="M14" s="17"/>
+      <c r="N14" s="17"/>
+      <c r="O14" s="17"/>
+      <c r="P14" s="17"/>
+      <c r="Q14" s="17"/>
+      <c r="R14" s="17"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q1"/>
+  <autoFilter ref="A1:R14"/>
   <mergeCells count="24">
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
-    <mergeCell ref="L2:L3"/>
     <mergeCell ref="M2:M3"/>
     <mergeCell ref="N2:N3"/>
     <mergeCell ref="O2:O3"/>
     <mergeCell ref="P2:P3"/>
     <mergeCell ref="Q2:Q3"/>
+    <mergeCell ref="R2:R3"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="B10:B11"/>
-    <mergeCell ref="L10:L11"/>
     <mergeCell ref="M10:M11"/>
     <mergeCell ref="N10:N11"/>
     <mergeCell ref="O10:O11"/>
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="Q10:Q11"/>
+    <mergeCell ref="R10:R11"/>
     <mergeCell ref="A13:A14"/>
     <mergeCell ref="B13:B14"/>
-    <mergeCell ref="L13:L14"/>
     <mergeCell ref="M13:M14"/>
     <mergeCell ref="N13:N14"/>
     <mergeCell ref="O13:O14"/>
     <mergeCell ref="P13:P14"/>
     <mergeCell ref="Q13:Q14"/>
+    <mergeCell ref="R13:R14"/>
   </mergeCells>
   <dataValidations count="8">
     <dataValidation type="list" allowBlank="1" sqref="H10:H14">
@@ -1651,16 +1747,16 @@
     <dataValidation type="list" allowBlank="1" sqref="H8:H14">
       <formula1>"verifisert,delvis,sekundær,ikke funnet,feil"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J10:J14">
+    <dataValidation type="list" allowBlank="1" sqref="K10:K14">
       <formula1>"ja,nei,preprint"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J2:J14">
+    <dataValidation type="list" allowBlank="1" sqref="K2:K14">
       <formula1>"ja,nei,preprint"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L10:P14">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="M10:Q14">
       <formula1>"0,1,2,3"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L2:P14">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="M2:Q14">
       <formula1>"0,1,2,3"</formula1>
     </dataValidation>
   </dataValidations>
